--- a/2024国赛A题/附件/result4_paper.xlsx
+++ b/2024国赛A题/附件/result4_paper.xlsx
@@ -1,43 +1,1120 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="25600" windowHeight="12080" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="位置" sheetId="1" r:id="rId1"/>
+    <sheet name="速度" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="26">
+  <si>
+    <t>-100 s</t>
+  </si>
+  <si>
+    <t>-50 s</t>
+  </si>
+  <si>
+    <t>0 s</t>
+  </si>
+  <si>
+    <t>50 s</t>
+  </si>
+  <si>
+    <t>100 s</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>龙头</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>x (m)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>龙头</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>y (m)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>节龙身</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>x (m)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>节龙身</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>y (m)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>51</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>节龙身</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>x (m)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>51</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>节龙身</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>y (m)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>101</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>节龙身</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>x (m)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>101</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>节龙身</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>y (m)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>151</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>节龙身</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>x (m)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>151</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>节龙身</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>y (m)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>201</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>节龙身</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>x (m)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>201</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>节龙身</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>y (m)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>龙尾（后）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>x (m)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>龙尾（后）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>y (m)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>龙头</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> (m/s)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>节龙身</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">  (m/s)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>51</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>节龙身</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">  (m/s)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>101</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>节龙身</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">  (m/s)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>151</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>节龙身</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">  (m/s)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>201</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>节龙身</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">  (m/s)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>龙尾（后）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> (m/s)</t>
+    </r>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="26">
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
-    <fill>
-      <patternFill/>
+  <fills count="33">
+    <fill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -46,93 +1123,359 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="12">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -415,47 +1758,498 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="2" width="31.1818181818182" customWidth="1"/>
+    <col min="3" max="5" width="117.909090909091"/>
+    <col min="6" max="6" width="106.636363636364"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>名称</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>时刻(s)</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>x(m)</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>y(m)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>速度(m/s)</t>
-        </is>
+    <row r="1" spans="1:6">
+      <c r="A1" s="9"/>
+      <c r="B1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="4">
+        <v>7.778034</v>
+      </c>
+      <c r="C2" s="4">
+        <v>6.608301</v>
+      </c>
+      <c r="D2" s="4">
+        <v>-2.711856</v>
+      </c>
+      <c r="E2" s="5">
+        <v>1.332696</v>
+      </c>
+      <c r="F2" s="4">
+        <v>-2.817074</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="4">
+        <v>3.717164</v>
+      </c>
+      <c r="C3" s="4">
+        <v>1.898865</v>
+      </c>
+      <c r="D3" s="4">
+        <v>-3.591078</v>
+      </c>
+      <c r="E3" s="5">
+        <v>6.175324</v>
+      </c>
+      <c r="F3" s="4">
+        <v>7.669223</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="4">
+        <v>6.209273</v>
+      </c>
+      <c r="C4" s="4">
+        <v>5.366911</v>
+      </c>
+      <c r="D4" s="4">
+        <v>-0.063534</v>
+      </c>
+      <c r="E4" s="5">
+        <v>3.819749</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0.014063</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="1:6">
+      <c r="A5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="4">
+        <v>6.108521</v>
+      </c>
+      <c r="C5" s="4">
+        <v>4.475403</v>
+      </c>
+      <c r="D5" s="4">
+        <v>-4.670888</v>
+      </c>
+      <c r="E5" s="5">
+        <v>4.877561</v>
+      </c>
+      <c r="F5" s="4">
+        <v>8.074517</v>
+      </c>
+    </row>
+    <row r="6" ht="13" customHeight="1" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="4">
+        <v>-10.608038</v>
+      </c>
+      <c r="C6" s="4">
+        <v>-3.629945</v>
+      </c>
+      <c r="D6" s="4">
+        <v>2.459962</v>
+      </c>
+      <c r="E6" s="5">
+        <v>-2.256084</v>
+      </c>
+      <c r="F6" s="4">
+        <v>2.398395</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="4">
+        <v>2.831491</v>
+      </c>
+      <c r="C7" s="4">
+        <v>-8.9638</v>
+      </c>
+      <c r="D7" s="4">
+        <v>-7.778145</v>
+      </c>
+      <c r="E7" s="5">
+        <v>-5.855939</v>
+      </c>
+      <c r="F7" s="4">
+        <v>3.835693</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="4">
+        <v>-11.922761</v>
+      </c>
+      <c r="C8" s="4">
+        <v>10.125787</v>
+      </c>
+      <c r="D8" s="4">
+        <v>3.008493</v>
+      </c>
+      <c r="E8" s="5">
+        <v>-7.208242</v>
+      </c>
+      <c r="F8" s="5">
+        <v>9.025199</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="4">
+        <v>-4.802378</v>
+      </c>
+      <c r="C9" s="4">
+        <v>-5.972247</v>
+      </c>
+      <c r="D9" s="4">
+        <v>10.108539</v>
+      </c>
+      <c r="E9" s="5">
+        <v>5.667884</v>
+      </c>
+      <c r="F9" s="5">
+        <v>-4.478707</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="4">
+        <v>-14.351032</v>
+      </c>
+      <c r="C10" s="4">
+        <v>12.974784</v>
+      </c>
+      <c r="D10" s="4">
+        <v>-7.002789</v>
+      </c>
+      <c r="E10" s="5">
+        <v>-5.161822</v>
+      </c>
+      <c r="F10" s="4">
+        <v>10.092396</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="4">
+        <v>-1.980993</v>
+      </c>
+      <c r="C11" s="4">
+        <v>-3.810357</v>
+      </c>
+      <c r="D11" s="4">
+        <v>10.337482</v>
+      </c>
+      <c r="E11" s="5">
+        <v>-10.105202</v>
+      </c>
+      <c r="F11" s="4">
+        <v>-1.230782</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="4">
+        <v>-11.952942</v>
+      </c>
+      <c r="C12" s="4">
+        <v>10.522509</v>
+      </c>
+      <c r="D12" s="4">
+        <v>-6.872842</v>
+      </c>
+      <c r="E12" s="5">
+        <v>-0.286734</v>
+      </c>
+      <c r="F12" s="5">
+        <v>9.210831</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="4">
+        <v>10.566998</v>
+      </c>
+      <c r="C13" s="4">
+        <v>-10.807425</v>
+      </c>
+      <c r="D13" s="4">
+        <v>12.382609</v>
+      </c>
+      <c r="E13" s="5">
+        <v>-13.165987</v>
+      </c>
+      <c r="F13" s="5">
+        <v>7.832286</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="11">
+        <v>-1.011059</v>
+      </c>
+      <c r="C14" s="11">
+        <v>0.189809</v>
+      </c>
+      <c r="D14" s="11">
+        <v>-1.933627</v>
+      </c>
+      <c r="E14" s="5">
+        <v>6.413294</v>
+      </c>
+      <c r="F14" s="5">
+        <v>-11.468506</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="11">
+        <v>-16.527573</v>
+      </c>
+      <c r="C15" s="11">
+        <v>15.720588</v>
+      </c>
+      <c r="D15" s="11">
+        <v>-14.713128</v>
+      </c>
+      <c r="E15" s="5">
+        <v>12.326648</v>
+      </c>
+      <c r="F15" s="5">
+        <v>-5.857484</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="27.2727272727273" customWidth="1"/>
+    <col min="2" max="6" width="9.54545454545454"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="4">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4">
+        <v>1</v>
+      </c>
+      <c r="F2" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.999352</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.99635</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.983383</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0.995991</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0.999483</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.998996</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.996866</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.984884</v>
+      </c>
+      <c r="E4" s="5">
+        <v>1.022878</v>
+      </c>
+      <c r="F4" s="5">
+        <v>0.999499</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.998834</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.997048</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.985175</v>
+      </c>
+      <c r="E5" s="5">
+        <v>1.021318</v>
+      </c>
+      <c r="F5" s="5">
+        <v>1.060724</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0.998741</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0.997141</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0.985298</v>
+      </c>
+      <c r="E6" s="5">
+        <v>1.020845</v>
+      </c>
+      <c r="F6" s="5">
+        <v>1.059814</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="4">
+        <v>0.99868</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0.997197</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0.985367</v>
+      </c>
+      <c r="E7" s="5">
+        <v>1.020616</v>
+      </c>
+      <c r="F7" s="5">
+        <v>1.059459</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="7">
+        <v>0.998817</v>
+      </c>
+      <c r="C8" s="7">
+        <v>0.99788</v>
+      </c>
+      <c r="D8" s="7">
+        <v>1.019502</v>
+      </c>
+      <c r="E8" s="7">
+        <v>1.020551</v>
+      </c>
+      <c r="F8" s="7">
+        <v>1.059367</v>
+      </c>
+    </row>
+    <row r="14" spans="5:5">
+      <c r="E14" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>